--- a/products/store_b/out/08_Etsy_Seller_Bookkeeping.xlsx
+++ b/products/store_b/out/08_Etsy_Seller_Bookkeeping.xlsx
@@ -1381,11 +1381,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="22836228"/>
-        <c:axId val="67750607"/>
+        <c:axId val="17780844"/>
+        <c:axId val="91470359"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="22836228"/>
+        <c:axId val="17780844"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1417,7 +1417,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67750607"/>
+        <c:crossAx val="91470359"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1425,7 +1425,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="67750607"/>
+        <c:axId val="91470359"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1467,7 +1467,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="22836228"/>
+        <c:crossAx val="17780844"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1715,11 +1715,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="91873800"/>
-        <c:axId val="55031706"/>
+        <c:axId val="71080543"/>
+        <c:axId val="52010743"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="91873800"/>
+        <c:axId val="71080543"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1751,7 +1751,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="55031706"/>
+        <c:crossAx val="52010743"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1759,7 +1759,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="55031706"/>
+        <c:axId val="52010743"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1801,7 +1801,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="91873800"/>
+        <c:crossAx val="71080543"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
